--- a/data/Lop3/Toan/Toan_lop3.xlsx
+++ b/data/Lop3/Toan/Toan_lop3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\4.WEB\daubifamily.github.io-main\data\Lop3\Toan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5ADDB0DC-4178-43E9-9EBD-3A881AA48B70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C9C02C6-773E-41D6-B1D9-806B6114C95B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="10690" windowWidth="19420" windowHeight="10420" tabRatio="590" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="10690" windowWidth="19420" windowHeight="10420" tabRatio="590" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="De1" sheetId="1" r:id="rId1"/>
@@ -47,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="847">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1754" uniqueCount="1214">
   <si>
     <t>ID</t>
   </si>
@@ -2588,6 +2588,1107 @@
   </si>
   <si>
     <t>de4_q39.png</t>
+  </si>
+  <si>
+    <t>Tính giá trị (Arithmetic operations): 4153 x 6 = ?</t>
+  </si>
+  <si>
+    <t>A. 24818</t>
+  </si>
+  <si>
+    <t>B. 24918</t>
+  </si>
+  <si>
+    <t>C. 24718</t>
+  </si>
+  <si>
+    <t>D. 25918</t>
+  </si>
+  <si>
+    <t>Đặt tính nhân: 4153 x 6 = 24918 -&gt; Chọn B</t>
+  </si>
+  <si>
+    <t>Tính giá trị: 9545 : 5 = ?</t>
+  </si>
+  <si>
+    <t>A. 1919</t>
+  </si>
+  <si>
+    <t>B. 1809</t>
+  </si>
+  <si>
+    <t>C. 1909</t>
+  </si>
+  <si>
+    <t>D. 1819</t>
+  </si>
+  <si>
+    <t>Đặt tính chia: 9545 : 5 = 1909 -&gt; Chọn C</t>
+  </si>
+  <si>
+    <t>Tính: 3254 + 1405 x 5 = ?</t>
+  </si>
+  <si>
+    <t>A. 10179</t>
+  </si>
+  <si>
+    <t>B. 10379</t>
+  </si>
+  <si>
+    <t>C. 10279</t>
+  </si>
+  <si>
+    <t>D. 10479</t>
+  </si>
+  <si>
+    <t>Nhân trước cộng sau: 1405 x 5 = 7025; 3254 + 7025 = 10279 -&gt; Chọn C</t>
+  </si>
+  <si>
+    <t>Tính: (7245 - 3128) x 4 = ?</t>
+  </si>
+  <si>
+    <t>A. 16568</t>
+  </si>
+  <si>
+    <t>B. 16368</t>
+  </si>
+  <si>
+    <t>C. 16268</t>
+  </si>
+  <si>
+    <t>D. 16468</t>
+  </si>
+  <si>
+    <t>Tính trong ngoặc: 7245 - 3128 = 4117; 4117 x 4 = 16468 -&gt; Chọn D</t>
+  </si>
+  <si>
+    <t>Tính giá trị: 54900 : 9 = ?</t>
+  </si>
+  <si>
+    <t>A. 6100</t>
+  </si>
+  <si>
+    <t>B. 6200</t>
+  </si>
+  <si>
+    <t>D. 6300</t>
+  </si>
+  <si>
+    <t>Chia nhẩm: 54 chia 9 được 6, 9 chia 9 được 1, thêm 2 số 0 thành 6100 -&gt; Chọn A</t>
+  </si>
+  <si>
+    <t>Tìm số dư của phép chia (Division with remainder): 8564 : 6</t>
+  </si>
+  <si>
+    <t>C. 2</t>
+  </si>
+  <si>
+    <t>D. 1</t>
+  </si>
+  <si>
+    <t>8564 chia 6 được 1427 dư 2 -&gt; Chọn C</t>
+  </si>
+  <si>
+    <t>Tính: 524 + 68 x 7 = ?</t>
+  </si>
+  <si>
+    <t>A. 1020</t>
+  </si>
+  <si>
+    <t>B. 1100</t>
+  </si>
+  <si>
+    <t>C. 900</t>
+  </si>
+  <si>
+    <t>D. 1000</t>
+  </si>
+  <si>
+    <t>Nhân trước: 68 x 7 = 476; 524 + 476 = 1000 -&gt; Chọn D</t>
+  </si>
+  <si>
+    <t>Tính: 4000 - 350 x 8 = ?</t>
+  </si>
+  <si>
+    <t>B. 1200</t>
+  </si>
+  <si>
+    <t>D. 1600</t>
+  </si>
+  <si>
+    <t>Nhân trước: 350 x 8 = 2800; 4000 - 2800 = 1200 -&gt; Chọn B</t>
+  </si>
+  <si>
+    <t>Điền số thích hợp: ... x 7 = 8519</t>
+  </si>
+  <si>
+    <t>A. 1217</t>
+  </si>
+  <si>
+    <t>B. 1227</t>
+  </si>
+  <si>
+    <t>C. 1237</t>
+  </si>
+  <si>
+    <t>D. 1207</t>
+  </si>
+  <si>
+    <t>Tìm thừa số: 8519 : 7 = 1217 -&gt; Chọn A</t>
+  </si>
+  <si>
+    <t>Điền số thích hợp: 9632 : ... = 8</t>
+  </si>
+  <si>
+    <t>A. 1224</t>
+  </si>
+  <si>
+    <t>B. 1204</t>
+  </si>
+  <si>
+    <t>C. 1214</t>
+  </si>
+  <si>
+    <t>D. 1234</t>
+  </si>
+  <si>
+    <t>Tìm số chia: 9632 : 8 = 1204 -&gt; Chọn B</t>
+  </si>
+  <si>
+    <t>Đổi đơn vị (Unit conversion): 9kg 45g = ... g</t>
+  </si>
+  <si>
+    <t>A. 9045</t>
+  </si>
+  <si>
+    <t>B. 9450</t>
+  </si>
+  <si>
+    <t>C. 945</t>
+  </si>
+  <si>
+    <t>D. 90045</t>
+  </si>
+  <si>
+    <t>1kg = 1000g nên 9kg = 9000g; 9000g + 45g = 9045g -&gt; Chọn A</t>
+  </si>
+  <si>
+    <t>Đổi đơn vị: 7 giờ 15 phút = ... phút</t>
+  </si>
+  <si>
+    <t>B. 445</t>
+  </si>
+  <si>
+    <t>C. 435</t>
+  </si>
+  <si>
+    <t>D. 415</t>
+  </si>
+  <si>
+    <t>1 giờ = 60 phút nên 7 giờ = 420 phút; 420 + 15 = 435 phút -&gt; Chọn C</t>
+  </si>
+  <si>
+    <t>Tính chu vi hình vuông có cạnh 525cm.</t>
+  </si>
+  <si>
+    <t>A. 2200</t>
+  </si>
+  <si>
+    <t>B. 2100</t>
+  </si>
+  <si>
+    <t>C. 2300</t>
+  </si>
+  <si>
+    <t>Chu vi = Cạnh x 4: 525 x 4 = 2100 (cm) -&gt; Chọn B</t>
+  </si>
+  <si>
+    <t>Tính diện tích hình chữ nhật có chiều dài 48cm, chiều rộng 9cm.</t>
+  </si>
+  <si>
+    <t>A. 422</t>
+  </si>
+  <si>
+    <t>B. 452</t>
+  </si>
+  <si>
+    <t>C. 442</t>
+  </si>
+  <si>
+    <t>D. 432</t>
+  </si>
+  <si>
+    <t>Diện tích = Dài x Rộng: 48 x 9 = 432 (cm2) -&gt; Chọn D</t>
+  </si>
+  <si>
+    <t>Một phần bảy của 8547 là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>A. 1211</t>
+  </si>
+  <si>
+    <t>B. 1221</t>
+  </si>
+  <si>
+    <t>C. 1231</t>
+  </si>
+  <si>
+    <t>D. 1201</t>
+  </si>
+  <si>
+    <t>Lấy số đó chia cho 7: 8547 : 7 = 1221 -&gt; Chọn B</t>
+  </si>
+  <si>
+    <t>Gấp 515 lên 3 lần rồi trừ đi 220 ta được kết quả là?</t>
+  </si>
+  <si>
+    <t>A. 1325</t>
+  </si>
+  <si>
+    <t>B. 1335</t>
+  </si>
+  <si>
+    <t>C. 1315</t>
+  </si>
+  <si>
+    <t>D. 1345</t>
+  </si>
+  <si>
+    <t>515 x 3 = 1545; 1545 - 220 = 1325 -&gt; Chọn A</t>
+  </si>
+  <si>
+    <t>Giảm 2448 đi 8 lần rồi thêm 612 ta được kết quả là?</t>
+  </si>
+  <si>
+    <t>A. 928</t>
+  </si>
+  <si>
+    <t>B. 918</t>
+  </si>
+  <si>
+    <t>C. 938</t>
+  </si>
+  <si>
+    <t>D. 908</t>
+  </si>
+  <si>
+    <t>2448 : 8 = 306; 306 + 612 = 918 -&gt; Chọn B</t>
+  </si>
+  <si>
+    <t>Tính nhanh (Logical arithmetic): 642 x 7 - 342 x 7 = ?</t>
+  </si>
+  <si>
+    <t>A. 2000</t>
+  </si>
+  <si>
+    <t>B. 2200</t>
+  </si>
+  <si>
+    <t>C. 2100</t>
+  </si>
+  <si>
+    <t>D. 2300</t>
+  </si>
+  <si>
+    <t>Nhóm thừa số chung: (642 - 342) x 7 = 300 x 7 = 2100 -&gt; Chọn C</t>
+  </si>
+  <si>
+    <t>Tính nhanh: 720 : 8 + 240 : 8 = ?</t>
+  </si>
+  <si>
+    <t>A. 110</t>
+  </si>
+  <si>
+    <t>B. 120</t>
+  </si>
+  <si>
+    <t>Nhóm phép chia: (720 + 240) : 8 = 960 : 8 = 120 -&gt; Chọn B</t>
+  </si>
+  <si>
+    <t>Tìm x, biết x : 7 = 145 (dư 5)</t>
+  </si>
+  <si>
+    <t>A. 1015</t>
+  </si>
+  <si>
+    <t>B. 1025</t>
+  </si>
+  <si>
+    <t>C. 1020</t>
+  </si>
+  <si>
+    <t>D. 1010</t>
+  </si>
+  <si>
+    <t>Số bị chia = Thương x Số chia + Số dư: 145 x 7 + 5 = 1015 + 5 = 1020 -&gt; Chọn C</t>
+  </si>
+  <si>
+    <t>Cửa hàng có 450 quả cam. Đã bán 90 quả, số còn lại xếp vào các hộp, mỗi hộp 9 quả (Problem-solving). Hỏi xếp được bao nhiêu hộp?</t>
+  </si>
+  <si>
+    <t>Số cam còn lại: 450 - 90 = 360. Số hộp xếp được: 360 : 9 = 40 (hộp) -&gt; Chọn B</t>
+  </si>
+  <si>
+    <t>Mỗi ngày Lan đọc 25 trang truyện. Hỏi trong 3 tuần lễ Lan đọc được bao nhiêu trang?</t>
+  </si>
+  <si>
+    <t>A. 525</t>
+  </si>
+  <si>
+    <t>B. 515</t>
+  </si>
+  <si>
+    <t>C. 535</t>
+  </si>
+  <si>
+    <t>3 tuần = 21 ngày. Số trang: 25 x 21 = 525 (trang) -&gt; Chọn A</t>
+  </si>
+  <si>
+    <t>Một rạp chiếu phim có 18 hàng ghế (Array of Objects), mỗi hàng có 22 ghế. Hỏi rạp chiếu phim có tất cả bao nhiêu ghế?</t>
+  </si>
+  <si>
+    <t>A. 406</t>
+  </si>
+  <si>
+    <t>B. 386</t>
+  </si>
+  <si>
+    <t>C. 376</t>
+  </si>
+  <si>
+    <t>D. 396</t>
+  </si>
+  <si>
+    <t>Tổng số ghế: 18 x 22 = 396 (ghế) -&gt; Chọn D</t>
+  </si>
+  <si>
+    <t>Có 75 hộp kẹo, mỗi hộp có 1 tá kẹo. Hỏi có tất cả bao nhiêu chiếc kẹo?</t>
+  </si>
+  <si>
+    <t>A. 800</t>
+  </si>
+  <si>
+    <t>D. 950</t>
+  </si>
+  <si>
+    <t>1 tá = 12 chiếc. Tổng số kẹo: 75 x 12 = 900 (chiếc) -&gt; Chọn B</t>
+  </si>
+  <si>
+    <t>Một máy cày trong 15 phút cày được 12 mét vuông đất. Hỏi máy đó cày 60 mét vuông mất bao nhiêu phút?</t>
+  </si>
+  <si>
+    <t>A. 60</t>
+  </si>
+  <si>
+    <t>B. 90</t>
+  </si>
+  <si>
+    <t>C. 75</t>
+  </si>
+  <si>
+    <t>60m2 gấp 5 lần 12m2 (60:12=5). Thời gian gấp 5 lần: 15 x 5 = 75 phút -&gt; Chọn C</t>
+  </si>
+  <si>
+    <t>Có 215 cuốn sách. Một ngăn giá sách để được 8 cuốn. Hỏi cần ÍT NHẤT bao nhiêu ngăn để xếp hết số sách đó?</t>
+  </si>
+  <si>
+    <t>A. 27</t>
+  </si>
+  <si>
+    <t>D. 25</t>
+  </si>
+  <si>
+    <t>215 : 8 = 26 (dư 7 cuốn). Cần thêm 1 ngăn để xếp số sách dư nên 26 + 1 = 27 ngăn -&gt; Chọn A</t>
+  </si>
+  <si>
+    <t>Cần 45cm ruy-băng để làm 1 chiếc nơ. Từ 4 mét ruy-băng có thể làm được NHIỀU NHẤT bao nhiêu chiếc nơ?</t>
+  </si>
+  <si>
+    <t>4m = 400cm. Ta có 400 : 45 = 8 (dư 40cm). Làm được tối đa 8 chiếc -&gt; Chọn C</t>
+  </si>
+  <si>
+    <t>Bình tiết kiệm mỗi ngày cùng một số tiền. Sau 2 tuần Bình có 112000 đồng. Mỗi ngày Bình tiết kiệm bao nhiêu?</t>
+  </si>
+  <si>
+    <t>A. 9000</t>
+  </si>
+  <si>
+    <t>B. 7000</t>
+  </si>
+  <si>
+    <t>C. 10000</t>
+  </si>
+  <si>
+    <t>2 tuần = 14 ngày. Số tiền 1 ngày: 112000 : 14 = 8000 (đồng) -&gt; Chọn D</t>
+  </si>
+  <si>
+    <t>Hình chữ nhật có chu vi 108cm, chiều dài 35cm. Tính chiều rộng của hình chữ nhật.</t>
+  </si>
+  <si>
+    <t>A. 19</t>
+  </si>
+  <si>
+    <t>B. 17</t>
+  </si>
+  <si>
+    <t>C. 21</t>
+  </si>
+  <si>
+    <t>Nửa chu vi: 108 : 2 = 54. Chiều rộng: 54 - 35 = 19 (cm) -&gt; Chọn A</t>
+  </si>
+  <si>
+    <t>Mua 7 quyển vở hết 105000 đồng. Hỏi mua 4 quyển như thế hết bao nhiêu tiền?</t>
+  </si>
+  <si>
+    <t>A. 50000</t>
+  </si>
+  <si>
+    <t>B. 55000</t>
+  </si>
+  <si>
+    <t>D. 60000</t>
+  </si>
+  <si>
+    <t>Giá 1 quyển: 105000 : 7 = 15000. Giá 4 quyển: 15000 x 4 = 60000 -&gt; Chọn D</t>
+  </si>
+  <si>
+    <t>Hai số tự nhiên có tổng bằng 25 và tích bằng 144 (Logical reasoning). Số LỚN HƠN trong hai số đó là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>Hai số có tích 144 có thể là (12,12), (9,16)... Cặp có tổng 25 là (9, 16). Số lớn hơn là 16 -&gt; Chọn A</t>
+  </si>
+  <si>
+    <t>Quan sát 2 chiếc cân đĩa đang thăng bằng (Multi-step Logic scale). Hỏi 1 khối Vuông nặng bằng mấy khối Tam giác?</t>
+  </si>
+  <si>
+    <t>Cân 1: 2 Vuông = 1 Tròn + 1 Tam giác. Cân 2: 1 Tròn = 3 Tam giác. Thay (3 Tam giác) vào Tròn ở cân 1: 2 Vuông = (3 Tam giác) + 1 Tam giác = 4 Tam giác. Vậy 1 Vuông = 2 Tam giác -&gt; Chọn B</t>
+  </si>
+  <si>
+    <t>Quy luật (Pattern recognition): Biểu tượng bên trong (Mũi tên kép) xoay 45 độ theo chiều kim đồng hồ qua mỗi bước. Nếu ô 3 nằm ngang, ô 4 sẽ nằm nghiêng chéo xuống góc phải -&gt; Chọn Hình C -&gt; Chọn C</t>
+  </si>
+  <si>
+    <t>Tìm số điền vào chỗ trống trong dãy số: 5, 11, 23, 47, 95, ...?</t>
+  </si>
+  <si>
+    <t>A. 191</t>
+  </si>
+  <si>
+    <t>B. 189</t>
+  </si>
+  <si>
+    <t>C. 193</t>
+  </si>
+  <si>
+    <t>D. 195</t>
+  </si>
+  <si>
+    <t>Quy luật: Số sau = (Số trước x 2) + 1. Ví dụ 5x2+1=11; 11x2+1=23; 95x2+1=191 -&gt; Chọn A</t>
+  </si>
+  <si>
+    <t>Từ các chữ số 0, 5, 6, 9, có thể lập được bao nhiêu số CHẴN có 2 chữ số KHÁC NHAU (Combinatorics)?</t>
+  </si>
+  <si>
+    <t>Số chẵn kết thúc bằng 0 hoặc 6. Nếu đuôi 0: có 3 số (50, 60, 90). Nếu đuôi 6: có 2 số (56, 96) vì chữ số hàng chục không được là 0. Tổng: 3 + 2 = 5 số -&gt; Chọn C</t>
+  </si>
+  <si>
+    <t>Một đường chạy hình tròn có chu vi 420m. Người ta trồng các chậu cây cách đều nhau 15m. Hỏi có tất cả bao nhiêu chậu cây?</t>
+  </si>
+  <si>
+    <t>C. 27</t>
+  </si>
+  <si>
+    <t>D. 30</t>
+  </si>
+  <si>
+    <t>Trồng cây vòng tròn khép kín: Số cây = Số khoảng cách = 420 : 15 = 28 (cây) -&gt; Chọn B</t>
+  </si>
+  <si>
+    <t>Khi đặt một chiếc gương dọc theo đường đứt nét (Mirror reflection), hình ảnh phản chiếu qua gương của chữ "STAR" sẽ là hình nào dưới đây?</t>
+  </si>
+  <si>
+    <t>Tính chất phản chiếu (Visual accuracy): Thứ tự chữ sẽ bị lật ngược từ phải sang trái thành R-A-T-S. Trong đó, chữ R và S sẽ bị lật ngược chiều (viết ngược), chữ A và T giữ nguyên dáng -&gt; Chọn Hình B -&gt; Chọn B</t>
+  </si>
+  <si>
+    <t>Trong sân có thỏ và gà (Logical deduction). Đếm được 20 cái đầu và 62 cái chân. Hỏi có bao nhiêu con THỎ?</t>
+  </si>
+  <si>
+    <t>C. 11</t>
+  </si>
+  <si>
+    <t>D. 12</t>
+  </si>
+  <si>
+    <t>Giả sử tất cả là gà (2 chân) thì có 20x2=40 chân (thiếu 22 chân). Mỗi con thỏ (4 chân) hơn gà 2 chân. Số thỏ là 22:2=11 con -&gt; Chọn C</t>
+  </si>
+  <si>
+    <t>Cho một tờ giấy trong suốt có kẻ ô vuông (Hình 1). Nếu gấp nếp tờ giấy này làm đôi từ dưới lên trên (Folding overlapping), hình nhận được là hình nào?</t>
+  </si>
+  <si>
+    <t>Tư duy không gian (Visual spatial): Các hình vẽ ở nửa dưới sẽ lật úp ngược lên và đè vào nửa trên. Các chấm đen sẽ nằm chèn lên nhau tạo ra tổ hợp mới -&gt; Chọn Hình D -&gt; Chọn D</t>
+  </si>
+  <si>
+    <t>Một chiếc đồng hồ đang chạy CHẬM 10 phút. Hiện tại đồng hồ đang hiển thị 11 giờ 20 phút. Em có lịch hẹn vào lúc 11 giờ 45 phút (Trick time question). Hỏi thực tế em còn bao nhiêu phút nữa là đến giờ hẹn?</t>
+  </si>
+  <si>
+    <t>A. 15 phút</t>
+  </si>
+  <si>
+    <t>B. 25 phút</t>
+  </si>
+  <si>
+    <t>C. 5 phút</t>
+  </si>
+  <si>
+    <t>D. 35 phút</t>
+  </si>
+  <si>
+    <t>Đồng hồ chạy chậm nghĩa là giờ hiển thị đang bị lùi lại. Giờ thực tế hiện tại là 11g20 + 10 phút = 11 giờ 30 phút. Từ 11g30 đến 11g45 còn đúng 15 phút -&gt; Chọn A</t>
+  </si>
+  <si>
+    <t>de5_q32.png</t>
+  </si>
+  <si>
+    <t>de5_q33.png</t>
+  </si>
+  <si>
+    <t>de5_q37.png</t>
+  </si>
+  <si>
+    <t>de5_q39.png</t>
+  </si>
+  <si>
+    <t>Tính giá trị (Arithmetic operations): 5214 x 6 = ?</t>
+  </si>
+  <si>
+    <t>A. 31284</t>
+  </si>
+  <si>
+    <t>B. 31184</t>
+  </si>
+  <si>
+    <t>C. 31274</t>
+  </si>
+  <si>
+    <t>D. 31384</t>
+  </si>
+  <si>
+    <t>Đặt tính nhân: 5214 x 6 = 31284 -&gt; Chọn A</t>
+  </si>
+  <si>
+    <t>Tính giá trị: 7425 : 3 = ?</t>
+  </si>
+  <si>
+    <t>A. 2465</t>
+  </si>
+  <si>
+    <t>B. 2485</t>
+  </si>
+  <si>
+    <t>C. 2475</t>
+  </si>
+  <si>
+    <t>D. 2495</t>
+  </si>
+  <si>
+    <t>Đặt tính chia: 7425 : 3 = 2475 -&gt; Chọn C</t>
+  </si>
+  <si>
+    <t>Tính: 4125 + 1520 x 4 = ?</t>
+  </si>
+  <si>
+    <t>A. 10105</t>
+  </si>
+  <si>
+    <t>B. 10205</t>
+  </si>
+  <si>
+    <t>C. 10305</t>
+  </si>
+  <si>
+    <t>D. 10405</t>
+  </si>
+  <si>
+    <t>Nhân trước cộng sau: 1520 x 4 = 6080; 4125 + 6080 = 10205 -&gt; Chọn B</t>
+  </si>
+  <si>
+    <t>Tính: (8512 - 4216) x 5 = ?</t>
+  </si>
+  <si>
+    <t>A. 21480</t>
+  </si>
+  <si>
+    <t>B. 21580</t>
+  </si>
+  <si>
+    <t>C. 21380</t>
+  </si>
+  <si>
+    <t>D. 21680</t>
+  </si>
+  <si>
+    <t>Tính trong ngoặc: 8512 - 4216 = 4296; 4296 x 5 = 21480 -&gt; Chọn A</t>
+  </si>
+  <si>
+    <t>D. 8200</t>
+  </si>
+  <si>
+    <t>Chia nhẩm: 64 chia 8 được 8, 8 chia 8 được 1, thêm hai chữ số 0 thành 8100 -&gt; Chọn C</t>
+  </si>
+  <si>
+    <t>Tìm số dư của phép chia (Division with remainder): 7654 : 5</t>
+  </si>
+  <si>
+    <t>Tận cùng là 4, số chia hết cho 5 gần nhất là 7650. Vậy 7654 chia 5 dư 4 -&gt; Chọn D</t>
+  </si>
+  <si>
+    <t>Tính: 645 + 85 x 6 = ?</t>
+  </si>
+  <si>
+    <t>A. 1155</t>
+  </si>
+  <si>
+    <t>B. 1145</t>
+  </si>
+  <si>
+    <t>C. 1165</t>
+  </si>
+  <si>
+    <t>D. 1135</t>
+  </si>
+  <si>
+    <t>Nhân trước: 85 x 6 = 510; 645 + 510 = 1155 -&gt; Chọn A</t>
+  </si>
+  <si>
+    <t>Tính: 5000 - 450 x 8 = ?</t>
+  </si>
+  <si>
+    <t>A. 1300</t>
+  </si>
+  <si>
+    <t>B. 1500</t>
+  </si>
+  <si>
+    <t>Nhân trước: 450 x 8 = 3600; 5000 - 3600 = 1400 -&gt; Chọn C</t>
+  </si>
+  <si>
+    <t>Điền số thích hợp: ... x 6 = 9126</t>
+  </si>
+  <si>
+    <t>A. 1521</t>
+  </si>
+  <si>
+    <t>B. 1511</t>
+  </si>
+  <si>
+    <t>C. 1531</t>
+  </si>
+  <si>
+    <t>D. 1541</t>
+  </si>
+  <si>
+    <t>Tìm thừa số: 9126 : 6 = 1521 -&gt; Chọn A</t>
+  </si>
+  <si>
+    <t>Điền số thích hợp: 8421 : ... = 7</t>
+  </si>
+  <si>
+    <t>A. 1213</t>
+  </si>
+  <si>
+    <t>B. 1203</t>
+  </si>
+  <si>
+    <t>C. 1223</t>
+  </si>
+  <si>
+    <t>D. 1233</t>
+  </si>
+  <si>
+    <t>Tìm số chia: 8421 : 7 = 1203 -&gt; Chọn B</t>
+  </si>
+  <si>
+    <t>Đổi đơn vị (Unit conversion): 6kg 25g = ... g</t>
+  </si>
+  <si>
+    <t>A. 6250</t>
+  </si>
+  <si>
+    <t>B. 60025</t>
+  </si>
+  <si>
+    <t>C. 6025</t>
+  </si>
+  <si>
+    <t>D. 625</t>
+  </si>
+  <si>
+    <t>1kg = 1000g nên 6kg = 6000g; 6000g + 25g = 6025g -&gt; Chọn C</t>
+  </si>
+  <si>
+    <t>Đổi đơn vị: 8 giờ 20 phút = ... phút</t>
+  </si>
+  <si>
+    <t>B. 520</t>
+  </si>
+  <si>
+    <t>C. 510</t>
+  </si>
+  <si>
+    <t>1 giờ = 60 phút nên 8 giờ = 480 phút; 480 + 20 = 500 phút -&gt; Chọn D</t>
+  </si>
+  <si>
+    <t>Tính chu vi hình vuông có cạnh 615cm.</t>
+  </si>
+  <si>
+    <t>A. 2440</t>
+  </si>
+  <si>
+    <t>B. 2450</t>
+  </si>
+  <si>
+    <t>C. 2460</t>
+  </si>
+  <si>
+    <t>D. 2470</t>
+  </si>
+  <si>
+    <t>Chu vi = Cạnh x 4: 615 x 4 = 2460 (cm) -&gt; Chọn C</t>
+  </si>
+  <si>
+    <t>Tính diện tích hình chữ nhật có chiều dài 54cm, chiều rộng 8cm.</t>
+  </si>
+  <si>
+    <t>A. 432</t>
+  </si>
+  <si>
+    <t>B. 422</t>
+  </si>
+  <si>
+    <t>D. 452</t>
+  </si>
+  <si>
+    <t>Diện tích = Dài x Rộng: 54 x 8 = 432 (cm2) -&gt; Chọn A</t>
+  </si>
+  <si>
+    <t>Một phần tám của 9256 là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>A. 1147</t>
+  </si>
+  <si>
+    <t>B. 1157</t>
+  </si>
+  <si>
+    <t>C. 1167</t>
+  </si>
+  <si>
+    <t>D. 1177</t>
+  </si>
+  <si>
+    <t>Lấy số đó chia cho 8: 9256 : 8 = 1157 -&gt; Chọn B</t>
+  </si>
+  <si>
+    <t>Gấp 625 lên 4 lần rồi trừ đi 350 ta được kết quả là?</t>
+  </si>
+  <si>
+    <t>A. 2250</t>
+  </si>
+  <si>
+    <t>B. 2150</t>
+  </si>
+  <si>
+    <t>C. 2350</t>
+  </si>
+  <si>
+    <t>D. 2050</t>
+  </si>
+  <si>
+    <t>625 x 4 = 2500; 2500 - 350 = 2150 -&gt; Chọn B</t>
+  </si>
+  <si>
+    <t>Giảm 2168 đi 8 lần rồi thêm 425 ta được kết quả là?</t>
+  </si>
+  <si>
+    <t>A. 696</t>
+  </si>
+  <si>
+    <t>B. 686</t>
+  </si>
+  <si>
+    <t>C. 706</t>
+  </si>
+  <si>
+    <t>D. 676</t>
+  </si>
+  <si>
+    <t>2168 : 8 = 271; 271 + 425 = 696 -&gt; Chọn A</t>
+  </si>
+  <si>
+    <t>Tính nhanh (Logical arithmetic): 845 x 9 - 545 x 9 = ?</t>
+  </si>
+  <si>
+    <t>A. 2600</t>
+  </si>
+  <si>
+    <t>B. 2800</t>
+  </si>
+  <si>
+    <t>C. 2700</t>
+  </si>
+  <si>
+    <t>D. 2900</t>
+  </si>
+  <si>
+    <t>Nhóm thừa số chung: (845 - 545) x 9 = 300 x 9 = 2700 -&gt; Chọn C</t>
+  </si>
+  <si>
+    <t>Tính nhanh: 810 : 9 + 270 : 9 = ?</t>
+  </si>
+  <si>
+    <t>Nhóm phép chia: (810 + 270) : 9 = 1080 : 9 = 120 -&gt; Chọn B</t>
+  </si>
+  <si>
+    <t>Tìm x, biết x : 8 = 152 (dư 6)</t>
+  </si>
+  <si>
+    <t>A. 1222</t>
+  </si>
+  <si>
+    <t>B. 1212</t>
+  </si>
+  <si>
+    <t>C. 1232</t>
+  </si>
+  <si>
+    <t>D. 1202</t>
+  </si>
+  <si>
+    <t>Số bị chia = Thương x Số chia + Số dư: 152 x 8 + 6 = 1216 + 6 = 1222 -&gt; Chọn A</t>
+  </si>
+  <si>
+    <t>Cô giáo có 540 viên kẹo. Cô cho các bạn 60 viên, số còn lại chia đều vào 8 hộp (Problem-solving). Mỗi hộp có bao nhiêu viên?</t>
+  </si>
+  <si>
+    <t>A. 50</t>
+  </si>
+  <si>
+    <t>B. 70</t>
+  </si>
+  <si>
+    <t>C. 55</t>
+  </si>
+  <si>
+    <t>Số kẹo còn lại: 540 - 60 = 480. Mỗi hộp có: 480 : 8 = 60 (viên) -&gt; Chọn D</t>
+  </si>
+  <si>
+    <t>Mỗi ngày An đọc 35 trang sách. Hỏi trong 4 tuần lễ An đọc được bao nhiêu trang?</t>
+  </si>
+  <si>
+    <t>A. 980</t>
+  </si>
+  <si>
+    <t>B. 970</t>
+  </si>
+  <si>
+    <t>C. 990</t>
+  </si>
+  <si>
+    <t>D. 960</t>
+  </si>
+  <si>
+    <t>4 tuần = 28 ngày. Số trang: 35 x 28 = 980 (trang) -&gt; Chọn A</t>
+  </si>
+  <si>
+    <t>Một hội trường có 16 hàng ghế (Array of Objects), mỗi hàng có 25 ghế. Hỏi hội trường có tất cả bao nhiêu ghế?</t>
+  </si>
+  <si>
+    <t>B. 400</t>
+  </si>
+  <si>
+    <t>C. 420</t>
+  </si>
+  <si>
+    <t>D. 440</t>
+  </si>
+  <si>
+    <t>Tổng số ghế: 16 x 25 = 400 (ghế) -&gt; Chọn B</t>
+  </si>
+  <si>
+    <t>Có 85 hộp bút, mỗi hộp có 1 tá bút. Hỏi có tất cả bao nhiêu chiếc bút?</t>
+  </si>
+  <si>
+    <t>B. 1040</t>
+  </si>
+  <si>
+    <t>D. 1080</t>
+  </si>
+  <si>
+    <t>1 tá = 12 chiếc. Tổng số bút: 85 x 12 = 1020 (chiếc) -&gt; Chọn A</t>
+  </si>
+  <si>
+    <t>Một máy bơm trong 8 phút bơm được 120 lít nước. Hỏi máy đó bơm 450 lít nước mất bao nhiêu phút?</t>
+  </si>
+  <si>
+    <t>B. 30</t>
+  </si>
+  <si>
+    <t>C. 35</t>
+  </si>
+  <si>
+    <t>1 phút bơm được: 120 : 8 = 15 lít. 450 lít cần: 450 : 15 = 30 phút -&gt; Chọn B</t>
+  </si>
+  <si>
+    <t>Có 250 cuốn sách. Một ngăn giá sách để được 9 cuốn. Hỏi cần ÍT NHẤT bao nhiêu ngăn để xếp hết số sách đó?</t>
+  </si>
+  <si>
+    <t>D. 29</t>
+  </si>
+  <si>
+    <t>250 : 9 = 27 (dư 7 cuốn). Cần thêm 1 ngăn cho số dư nên 27 + 1 = 28 ngăn -&gt; Chọn C</t>
+  </si>
+  <si>
+    <t>Cần 55cm ruy-băng để làm 1 chiếc nơ. Từ 5 mét ruy-băng có thể làm được NHIỀU NHẤT bao nhiêu chiếc nơ?</t>
+  </si>
+  <si>
+    <t>5m = 500cm. Ta có 500 : 55 = 9 (dư 5cm). Làm được tối đa 9 chiếc -&gt; Chọn B</t>
+  </si>
+  <si>
+    <t>Bình tiết kiệm mỗi ngày cùng một số tiền. Sau 3 tuần Bình có 105000 đồng. Mỗi ngày Bình tiết kiệm bao nhiêu?</t>
+  </si>
+  <si>
+    <t>A. 4000</t>
+  </si>
+  <si>
+    <t>B. 5000</t>
+  </si>
+  <si>
+    <t>D. 7000</t>
+  </si>
+  <si>
+    <t>3 tuần = 21 ngày. Số tiền 1 ngày: 105000 : 21 = 5000 (đồng) -&gt; Chọn B</t>
+  </si>
+  <si>
+    <t>Hình chữ nhật có chu vi 124cm, chiều dài 42cm. Tính chiều rộng của hình chữ nhật.</t>
+  </si>
+  <si>
+    <t>B. 20</t>
+  </si>
+  <si>
+    <t>C. 22</t>
+  </si>
+  <si>
+    <t>Nửa chu vi: 124 : 2 = 62. Chiều rộng: 62 - 42 = 20 (cm) -&gt; Chọn B</t>
+  </si>
+  <si>
+    <t>Mua 9 quyển vở hết 135000 đồng. Hỏi mua 6 quyển như thế hết bao nhiêu tiền?</t>
+  </si>
+  <si>
+    <t>A. 90000</t>
+  </si>
+  <si>
+    <t>B. 85000</t>
+  </si>
+  <si>
+    <t>C. 95000</t>
+  </si>
+  <si>
+    <t>D. 80000</t>
+  </si>
+  <si>
+    <t>Giá 1 quyển: 135000 : 9 = 15000. Giá 6 quyển: 15000 x 6 = 90000 -&gt; Chọn A</t>
+  </si>
+  <si>
+    <t>Hai số tự nhiên có tổng bằng 27 và tích bằng 180 (Logical reasoning). Số LỚN HƠN trong hai số đó là bao nhiêu?</t>
+  </si>
+  <si>
+    <t>D. 15</t>
+  </si>
+  <si>
+    <t>Hai số có tích 180 có thể là (10,18), (12,15). Cặp có tổng 27 là (12, 15). Số lớn hơn là 15 -&gt; Chọn D</t>
+  </si>
+  <si>
+    <t>Quan sát thông tin từ 2 chiếc cân đĩa đang thăng bằng (Multi-step Logic scale). Hỏi 1 khối Tròn và 1 khối Tam giác cộng lại sẽ nặng bằng mấy khối Vuông?</t>
+  </si>
+  <si>
+    <t>Cân 1: 1 Tam giác = 2 Vuông. Cân 2: 1 Tròn = 1 Tam giác + 1 Vuông. Thay thế: 1 Tròn = (2 Vuông) + 1 Vuông = 3 Vuông. Tổng (Tròn + Tam giác) = 3 Vuông + 2 Vuông = 5 Vuông -&gt; Chọn C</t>
+  </si>
+  <si>
+    <t>Quy luật (Pattern recognition): Hình lục giác bên trong có 1 cạnh được tô đậm. Cạnh tô đậm di chuyển luân phiên 2 bước theo chiều kim đồng hồ qua mỗi hình -&gt; Chọn Hình B -&gt; Chọn B</t>
+  </si>
+  <si>
+    <t>Tìm số điền vào chỗ trống trong dãy số: 3, 10, 31, 94, ...?</t>
+  </si>
+  <si>
+    <t>A. 280</t>
+  </si>
+  <si>
+    <t>B. 282</t>
+  </si>
+  <si>
+    <t>C. 283</t>
+  </si>
+  <si>
+    <t>D. 285</t>
+  </si>
+  <si>
+    <t>Quy luật: Số sau = (Số trước x 3) + 1. Ví dụ 3x3+1=10; 10x3+1=31; 94x3+1=283 -&gt; Chọn C</t>
+  </si>
+  <si>
+    <t>Từ các chữ số 0, 2, 5, 7, có thể lập được bao nhiêu số LẺ có 2 chữ số KHÁC NHAU (Combinatorics)?</t>
+  </si>
+  <si>
+    <t>Số lẻ kết thúc bằng 5 hoặc 7. Đuôi 5: có 2 số (25, 75). Đuôi 7: có 2 số (27, 57). Hàng chục không được là 0. Tổng: 2 + 2 = 4 số -&gt; Chọn B</t>
+  </si>
+  <si>
+    <t>Một đường chạy hình tròn có chu vi 480m. Người ta cắm các lá cờ cách đều nhau 12m. Hỏi có tất cả bao nhiêu lá cờ?</t>
+  </si>
+  <si>
+    <t>A. 39</t>
+  </si>
+  <si>
+    <t>Trồng cờ vòng tròn khép kín: Số cờ = Số khoảng cách = 480 : 12 = 40 (cờ) -&gt; Chọn B</t>
+  </si>
+  <si>
+    <t>Khi đặt một chiếc gương dọc theo đường đứt nét (Mirror reflection), hình ảnh phản chiếu qua gương của chữ "MOON" sẽ là hình nào dưới đây?</t>
+  </si>
+  <si>
+    <t>Tính chất phản chiếu (Visual accuracy): Chữ bị lật ngược từ phải sang trái thành "NOOM". Chữ M và O đối xứng dọc nên giữ nguyên, nhưng chữ N phải bị lật ngược nét chéo -&gt; Chọn Hình C -&gt; Chọn C</t>
+  </si>
+  <si>
+    <t>Trong một nông trại có bò và vịt (Logical deduction). Đếm được 22 cái đầu và 70 cái chân. Hỏi nông trại có bao nhiêu con VỊT?</t>
+  </si>
+  <si>
+    <t>Giả sử tất cả là bò (4 chân) thì có 22x4=88 chân (thừa 18 chân). Mỗi con bò hơn vịt 2 chân. Số vịt là 18:2=9 con -&gt; Chọn A</t>
+  </si>
+  <si>
+    <t>Cho một tờ giấy trong suốt có kẻ ô vuông (Hình 1). Nếu gấp nếp tờ giấy này làm đôi từ cạnh TRÁI sang cạnh PHẢI (Folding overlapping), hình nhận được là hình nào?</t>
+  </si>
+  <si>
+    <t>Tư duy không gian (Visual spatial): Các hình vẽ ở nửa bên trái sẽ lật úp đè lên nửa bên phải như động tác gập sách. Các chấm ở góc trái sẽ nằm đối xứng sang góc phải -&gt; Chọn Hình A -&gt; Chọn A</t>
+  </si>
+  <si>
+    <t>Đồng hồ của Nam đang chạy NHANH 15 phút. Hiện tại đồng hồ đang chỉ 10 giờ 20 phút. Nam có lịch học bơi vào lúc 10 giờ 30 phút (Trick time question). Hỏi thực tế Nam còn bao nhiêu phút nữa mới đến giờ học bơi?</t>
+  </si>
+  <si>
+    <t>A. 10 phút</t>
+  </si>
+  <si>
+    <t>D. 15 phút</t>
+  </si>
+  <si>
+    <t>Đồng hồ chạy nhanh nghĩa là nó hiển thị thời gian đã vượt lên trước. Giờ thực tế là 10g20 - 15 phút = 10 giờ 05 phút. Từ 10g05 đến 10g30 còn 25 phút -&gt; Chọn B</t>
+  </si>
+  <si>
+    <t>de6_q32.png</t>
+  </si>
+  <si>
+    <t>de6_q33.png</t>
+  </si>
+  <si>
+    <t>de6_q37.png</t>
+  </si>
+  <si>
+    <t>de6_q39.png</t>
   </si>
 </sst>
 </file>
@@ -2949,7 +4050,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -2976,7 +4077,7 @@
       </c>
       <c r="I2" s="3"/>
     </row>
-    <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -3003,7 +4104,7 @@
       </c>
       <c r="I3" s="5"/>
     </row>
-    <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>3</v>
       </c>
@@ -3030,7 +4131,7 @@
       </c>
       <c r="I4" s="3"/>
     </row>
-    <row r="5" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -3057,7 +4158,7 @@
       </c>
       <c r="I5" s="5"/>
     </row>
-    <row r="6" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>5</v>
       </c>
@@ -3084,7 +4185,7 @@
       </c>
       <c r="I6" s="3"/>
     </row>
-    <row r="7" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -3111,7 +4212,7 @@
       </c>
       <c r="I7" s="5"/>
     </row>
-    <row r="8" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>7</v>
       </c>
@@ -3138,7 +4239,7 @@
       </c>
       <c r="I8" s="3"/>
     </row>
-    <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -3219,7 +4320,7 @@
       </c>
       <c r="I11" s="5"/>
     </row>
-    <row r="12" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -3246,7 +4347,7 @@
       </c>
       <c r="I12" s="3"/>
     </row>
-    <row r="13" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -3273,7 +4374,7 @@
       </c>
       <c r="I13" s="5"/>
     </row>
-    <row r="14" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>13</v>
       </c>
@@ -3300,7 +4401,7 @@
       </c>
       <c r="I14" s="3"/>
     </row>
-    <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -3327,7 +4428,7 @@
       </c>
       <c r="I15" s="5"/>
     </row>
-    <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>15</v>
       </c>
@@ -3408,7 +4509,7 @@
       </c>
       <c r="I18" s="3"/>
     </row>
-    <row r="19" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>18</v>
       </c>
@@ -3435,7 +4536,7 @@
       </c>
       <c r="I19" s="5"/>
     </row>
-    <row r="20" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>19</v>
       </c>
@@ -18264,7 +19365,7 @@
       </c>
       <c r="I6" s="3"/>
     </row>
-    <row r="7" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -18480,7 +19581,7 @@
       </c>
       <c r="I14" s="3"/>
     </row>
-    <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -23739,7 +24840,7 @@
       </c>
       <c r="I6" s="3"/>
     </row>
-    <row r="7" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -23955,7 +25056,7 @@
       </c>
       <c r="I14" s="3"/>
     </row>
-    <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" ht="26.4" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>14</v>
       </c>
@@ -25652,352 +26753,1127 @@
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
-    <col min="2" max="2" width="45" customWidth="1"/>
+    <col min="2" max="2" width="178.21875" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="8" max="8" width="177.88671875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="35" customWidth="1"/>
     <col min="10" max="25" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>847</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>848</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>850</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>851</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>849</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>852</v>
+      </c>
       <c r="I2" s="3"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>853</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>854</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>855</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>856</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>857</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>856</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>858</v>
+      </c>
       <c r="I3" s="5"/>
     </row>
     <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>859</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>860</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>861</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>863</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>862</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>864</v>
+      </c>
       <c r="I4" s="3"/>
     </row>
     <row r="5" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>865</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>866</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>867</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>868</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>869</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>869</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>870</v>
+      </c>
       <c r="I5" s="5"/>
     </row>
     <row r="6" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>873</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>874</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>872</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>875</v>
+      </c>
       <c r="I6" s="3"/>
     </row>
     <row r="7" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>876</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>877</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>878</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>877</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>879</v>
+      </c>
       <c r="I7" s="5"/>
     </row>
     <row r="8" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>880</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>881</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>882</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>883</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>884</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>884</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>885</v>
+      </c>
       <c r="I8" s="3"/>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>886</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>887</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>888</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>887</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>889</v>
+      </c>
       <c r="I9" s="5"/>
     </row>
     <row r="10" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>890</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>891</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>892</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>893</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>894</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>891</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>895</v>
+      </c>
       <c r="I10" s="3"/>
     </row>
     <row r="11" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="4"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>896</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>897</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>898</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>899</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>900</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>898</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>901</v>
+      </c>
       <c r="I11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>902</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>903</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>904</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>905</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>906</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>903</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>907</v>
+      </c>
       <c r="I12" s="3"/>
     </row>
     <row r="13" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="4"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>908</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>909</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>910</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>911</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>910</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>912</v>
+      </c>
       <c r="I13" s="5"/>
     </row>
     <row r="14" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>913</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>914</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>916</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>915</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>917</v>
+      </c>
       <c r="I14" s="3"/>
     </row>
     <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="4"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>918</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>919</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>920</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>921</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>922</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>922</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>923</v>
+      </c>
       <c r="I15" s="5"/>
     </row>
     <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>924</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>925</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>926</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>927</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>928</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>926</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>929</v>
+      </c>
       <c r="I16" s="3"/>
     </row>
     <row r="17" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="4"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>930</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>931</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>932</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>933</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>934</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>931</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>935</v>
+      </c>
       <c r="I17" s="5"/>
     </row>
     <row r="18" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>936</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>937</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>938</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>939</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>940</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>938</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>941</v>
+      </c>
       <c r="I18" s="3"/>
     </row>
     <row r="19" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
+      <c r="A19" s="4">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>942</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>943</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>944</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>945</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>946</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>945</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>947</v>
+      </c>
       <c r="I19" s="5"/>
     </row>
     <row r="20" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>948</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>949</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>950</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>950</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>951</v>
+      </c>
       <c r="I20" s="3"/>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
+      <c r="A21" s="4">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>952</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>953</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>954</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>955</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>956</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>955</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>957</v>
+      </c>
       <c r="I21" s="5"/>
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>958</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>959</v>
+      </c>
       <c r="I22" s="3"/>
     </row>
     <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="4"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
+      <c r="A23" s="4">
+        <v>22</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>960</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>961</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>962</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>963</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>961</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>964</v>
+      </c>
       <c r="I23" s="5"/>
     </row>
     <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="2"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>965</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>966</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>967</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>968</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>969</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>970</v>
+      </c>
       <c r="I24" s="3"/>
     </row>
     <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="4"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
+      <c r="A25" s="4">
+        <v>24</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>971</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>972</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>506</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>973</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>564</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>974</v>
+      </c>
       <c r="I25" s="5"/>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>975</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>976</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>977</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>978</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>979</v>
+      </c>
       <c r="I26" s="3"/>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="4"/>
+      <c r="A27" s="4">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>980</v>
+      </c>
+      <c r="C27" t="s">
+        <v>981</v>
+      </c>
+      <c r="D27" t="s">
+        <v>827</v>
+      </c>
+      <c r="E27" t="s">
+        <v>456</v>
+      </c>
+      <c r="F27" t="s">
+        <v>982</v>
+      </c>
+      <c r="G27" t="s">
+        <v>981</v>
+      </c>
+      <c r="H27" t="s">
+        <v>983</v>
+      </c>
     </row>
     <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="4"/>
+      <c r="A28" s="4">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>984</v>
+      </c>
+      <c r="C28" t="s">
+        <v>36</v>
+      </c>
+      <c r="D28" t="s">
+        <v>57</v>
+      </c>
+      <c r="E28" t="s">
+        <v>15</v>
+      </c>
+      <c r="F28" t="s">
+        <v>27</v>
+      </c>
+      <c r="G28" t="s">
+        <v>15</v>
+      </c>
+      <c r="H28" t="s">
+        <v>985</v>
+      </c>
     </row>
     <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="4"/>
+      <c r="A29" s="4">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>986</v>
+      </c>
+      <c r="C29" t="s">
+        <v>987</v>
+      </c>
+      <c r="D29" t="s">
+        <v>988</v>
+      </c>
+      <c r="E29" t="s">
+        <v>989</v>
+      </c>
+      <c r="F29" t="s">
+        <v>111</v>
+      </c>
+      <c r="G29" t="s">
+        <v>111</v>
+      </c>
+      <c r="H29" t="s">
+        <v>990</v>
+      </c>
     </row>
     <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="4"/>
+      <c r="A30" s="4">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>991</v>
+      </c>
+      <c r="C30" t="s">
+        <v>992</v>
+      </c>
+      <c r="D30" t="s">
+        <v>993</v>
+      </c>
+      <c r="E30" t="s">
+        <v>994</v>
+      </c>
+      <c r="F30" t="s">
+        <v>47</v>
+      </c>
+      <c r="G30" t="s">
+        <v>992</v>
+      </c>
+      <c r="H30" t="s">
+        <v>995</v>
+      </c>
     </row>
     <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="4"/>
+      <c r="A31" s="4">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>996</v>
+      </c>
+      <c r="C31" t="s">
+        <v>997</v>
+      </c>
+      <c r="D31" t="s">
+        <v>998</v>
+      </c>
+      <c r="E31" t="s">
+        <v>810</v>
+      </c>
+      <c r="F31" t="s">
+        <v>999</v>
+      </c>
+      <c r="G31" t="s">
+        <v>999</v>
+      </c>
+      <c r="H31" t="s">
+        <v>1000</v>
+      </c>
     </row>
     <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="4"/>
-    </row>
-    <row r="33" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="4"/>
-    </row>
-    <row r="34" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="4"/>
-    </row>
-    <row r="35" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="4"/>
-    </row>
-    <row r="36" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="4"/>
-    </row>
-    <row r="37" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="4"/>
-    </row>
-    <row r="38" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="4"/>
-    </row>
-    <row r="39" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="4"/>
-    </row>
-    <row r="40" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="4"/>
-    </row>
-    <row r="41" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="4"/>
-    </row>
-    <row r="42" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="43" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="44" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="45" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="46" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="47" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="48" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="A32" s="4">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C32" t="s">
+        <v>805</v>
+      </c>
+      <c r="D32" t="s">
+        <v>22</v>
+      </c>
+      <c r="E32" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" t="s">
+        <v>9</v>
+      </c>
+      <c r="G32" t="s">
+        <v>805</v>
+      </c>
+      <c r="H32" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="4">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C33" t="s">
+        <v>42</v>
+      </c>
+      <c r="D33" t="s">
+        <v>30</v>
+      </c>
+      <c r="E33" t="s">
+        <v>49</v>
+      </c>
+      <c r="F33" t="s">
+        <v>32</v>
+      </c>
+      <c r="G33" t="s">
+        <v>30</v>
+      </c>
+      <c r="H33" t="s">
+        <v>1004</v>
+      </c>
+      <c r="I33" t="s">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="4">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>627</v>
+      </c>
+      <c r="C34" t="s">
+        <v>628</v>
+      </c>
+      <c r="D34" t="s">
+        <v>629</v>
+      </c>
+      <c r="E34" t="s">
+        <v>630</v>
+      </c>
+      <c r="F34" t="s">
+        <v>631</v>
+      </c>
+      <c r="G34" t="s">
+        <v>630</v>
+      </c>
+      <c r="H34" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I34" t="s">
+        <v>1033</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="4">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1008</v>
+      </c>
+      <c r="E35" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F35" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G35" t="s">
+        <v>1007</v>
+      </c>
+      <c r="H35" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="4">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C36" t="s">
+        <v>13</v>
+      </c>
+      <c r="D36" t="s">
+        <v>67</v>
+      </c>
+      <c r="E36" t="s">
+        <v>68</v>
+      </c>
+      <c r="F36" t="s">
+        <v>76</v>
+      </c>
+      <c r="G36" t="s">
+        <v>68</v>
+      </c>
+      <c r="H36" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="4">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C37" t="s">
+        <v>450</v>
+      </c>
+      <c r="D37" t="s">
+        <v>461</v>
+      </c>
+      <c r="E37" t="s">
+        <v>1015</v>
+      </c>
+      <c r="F37" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G37" t="s">
+        <v>461</v>
+      </c>
+      <c r="H37" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="4">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C38" t="s">
+        <v>628</v>
+      </c>
+      <c r="D38" t="s">
+        <v>629</v>
+      </c>
+      <c r="E38" t="s">
+        <v>630</v>
+      </c>
+      <c r="F38" t="s">
+        <v>631</v>
+      </c>
+      <c r="G38" t="s">
+        <v>629</v>
+      </c>
+      <c r="H38" t="s">
+        <v>1019</v>
+      </c>
+      <c r="I38" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="4">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1020</v>
+      </c>
+      <c r="C39" t="s">
+        <v>251</v>
+      </c>
+      <c r="D39" t="s">
+        <v>7</v>
+      </c>
+      <c r="E39" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F39" t="s">
+        <v>1022</v>
+      </c>
+      <c r="G39" t="s">
+        <v>1021</v>
+      </c>
+      <c r="H39" t="s">
+        <v>1023</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="4">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C40" t="s">
+        <v>628</v>
+      </c>
+      <c r="D40" t="s">
+        <v>629</v>
+      </c>
+      <c r="E40" t="s">
+        <v>630</v>
+      </c>
+      <c r="F40" t="s">
+        <v>631</v>
+      </c>
+      <c r="G40" t="s">
+        <v>631</v>
+      </c>
+      <c r="H40" t="s">
+        <v>1025</v>
+      </c>
+      <c r="I40" t="s">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="4">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1026</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1027</v>
+      </c>
+      <c r="D41" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E41" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F41" t="s">
+        <v>1030</v>
+      </c>
+      <c r="G41" t="s">
+        <v>1027</v>
+      </c>
+      <c r="H41" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="43" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="45" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="46" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="48" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -26965,349 +28841,1124 @@
     <col min="2" max="2" width="45" customWidth="1"/>
     <col min="3" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="22" customWidth="1"/>
-    <col min="8" max="8" width="40" customWidth="1"/>
+    <col min="8" max="8" width="170.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="35" customWidth="1"/>
     <col min="10" max="25" width="8.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A1" s="1"/>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="2" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A2" s="2"/>
-      <c r="B2" s="3"/>
-      <c r="C2" s="3"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="G2" s="3"/>
-      <c r="H2" s="3"/>
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>1040</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>1037</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>1041</v>
+      </c>
       <c r="I2" s="3"/>
     </row>
     <row r="3" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="4"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>1043</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>1044</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>1046</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>1045</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>1047</v>
+      </c>
       <c r="I3" s="5"/>
     </row>
     <row r="4" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A4" s="2"/>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>1049</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>1051</v>
+      </c>
+      <c r="F4" s="3" t="s">
+        <v>1052</v>
+      </c>
+      <c r="G4" s="3" t="s">
+        <v>1050</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>1053</v>
+      </c>
       <c r="I4" s="3"/>
     </row>
     <row r="5" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="4"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
+      <c r="A5" s="4">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>1054</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>1055</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>1056</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>1057</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>1058</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>1055</v>
+      </c>
+      <c r="H5" s="5" t="s">
+        <v>1059</v>
+      </c>
       <c r="I5" s="5"/>
     </row>
     <row r="6" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A6" s="2"/>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>1060</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>1061</v>
+      </c>
       <c r="I6" s="3"/>
     </row>
     <row r="7" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="4"/>
-      <c r="B7" s="5"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>1062</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="G7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="5" t="s">
+        <v>1063</v>
+      </c>
       <c r="I7" s="5"/>
     </row>
     <row r="8" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="2"/>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="A8" s="2">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>1064</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>1065</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>1066</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>1067</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>1068</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>1065</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>1069</v>
+      </c>
       <c r="I8" s="3"/>
     </row>
     <row r="9" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="4"/>
-      <c r="B9" s="5"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>1070</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>1072</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>888</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>584</v>
+      </c>
+      <c r="H9" s="5" t="s">
+        <v>1073</v>
+      </c>
       <c r="I9" s="5"/>
     </row>
     <row r="10" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A10" s="2"/>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="3"/>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3"/>
+      <c r="A10" s="2">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>1074</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>1076</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>1077</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>1078</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>1075</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>1079</v>
+      </c>
       <c r="I10" s="3"/>
     </row>
     <row r="11" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="4"/>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
+      <c r="A11" s="4">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>1082</v>
+      </c>
+      <c r="H11" s="5" t="s">
+        <v>1085</v>
+      </c>
       <c r="I11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="2"/>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="3"/>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="G12" s="3"/>
-      <c r="H12" s="3"/>
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>1086</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>1087</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>1088</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>1089</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>1090</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>1089</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>1091</v>
+      </c>
       <c r="I12" s="3"/>
     </row>
     <row r="13" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="4"/>
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5"/>
-      <c r="H13" s="5"/>
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>1093</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>510</v>
+      </c>
+      <c r="H13" s="5" t="s">
+        <v>1095</v>
+      </c>
       <c r="I13" s="5"/>
     </row>
     <row r="14" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="2"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="G14" s="3"/>
-      <c r="H14" s="3"/>
+      <c r="A14" s="2">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>1096</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>1097</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>1098</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>1099</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>1101</v>
+      </c>
       <c r="I14" s="3"/>
     </row>
     <row r="15" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="4"/>
-      <c r="B15" s="5"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-      <c r="F15" s="5"/>
-      <c r="G15" s="5"/>
-      <c r="H15" s="5"/>
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>1102</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>1103</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>1104</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>921</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G15" s="5" t="s">
+        <v>1103</v>
+      </c>
+      <c r="H15" s="5" t="s">
+        <v>1106</v>
+      </c>
       <c r="I15" s="5"/>
     </row>
     <row r="16" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="2"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
-      <c r="H16" s="3"/>
+      <c r="A16" s="2">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>1107</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>1108</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>1110</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>1109</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>1112</v>
+      </c>
       <c r="I16" s="3"/>
     </row>
     <row r="17" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A17" s="4"/>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="5"/>
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C17" s="5" t="s">
+        <v>1114</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>1115</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>1116</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>1117</v>
+      </c>
+      <c r="G17" s="5" t="s">
+        <v>1115</v>
+      </c>
+      <c r="H17" s="5" t="s">
+        <v>1118</v>
+      </c>
       <c r="I17" s="5"/>
     </row>
     <row r="18" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="2"/>
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-      <c r="D18" s="3"/>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="G18" s="3"/>
-      <c r="H18" s="3"/>
+      <c r="A18" s="2">
+        <v>17</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>1119</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>1120</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>1121</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>1122</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>1123</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>1124</v>
+      </c>
       <c r="I18" s="3"/>
     </row>
     <row r="19" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="4"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="5"/>
+      <c r="A19" s="4">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>1127</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>1128</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>1129</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>1128</v>
+      </c>
+      <c r="H19" s="5" t="s">
+        <v>1130</v>
+      </c>
       <c r="I19" s="5"/>
     </row>
     <row r="20" spans="1:9" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="2"/>
-      <c r="B20" s="3"/>
-      <c r="C20" s="3"/>
-      <c r="D20" s="3"/>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="G20" s="3"/>
-      <c r="H20" s="3"/>
+      <c r="A20" s="2">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>949</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>950</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>950</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>1132</v>
+      </c>
       <c r="I20" s="3"/>
     </row>
     <row r="21" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="4"/>
-      <c r="B21" s="5"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="5"/>
+      <c r="A21" s="4">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>1134</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>1136</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>1137</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>1134</v>
+      </c>
+      <c r="H21" s="5" t="s">
+        <v>1138</v>
+      </c>
       <c r="I21" s="5"/>
     </row>
     <row r="22" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="2"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
-      <c r="D22" s="3"/>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="G22" s="3"/>
-      <c r="H22" s="3"/>
+      <c r="A22" s="2">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>1139</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>1142</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>1143</v>
+      </c>
       <c r="I22" s="3"/>
     </row>
     <row r="23" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="4"/>
-      <c r="B23" s="5"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="5"/>
+      <c r="A23" s="4">
+        <v>22</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>1144</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>1145</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>1147</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G23" s="5" t="s">
+        <v>1145</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>1149</v>
+      </c>
       <c r="I23" s="5"/>
     </row>
     <row r="24" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="2"/>
-      <c r="B24" s="3"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="G24" s="3"/>
-      <c r="H24" s="3"/>
+      <c r="A24" s="2">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>1153</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>1151</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>1154</v>
+      </c>
       <c r="I24" s="3"/>
     </row>
     <row r="25" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="4"/>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
+      <c r="A25" s="4">
+        <v>24</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>1155</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>881</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>210</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>1157</v>
+      </c>
+      <c r="G25" s="5" t="s">
+        <v>881</v>
+      </c>
+      <c r="H25" s="5" t="s">
+        <v>1158</v>
+      </c>
       <c r="I25" s="5"/>
     </row>
     <row r="26" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="2"/>
-      <c r="B26" s="3"/>
-      <c r="C26" s="3"/>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="G26" s="3"/>
-      <c r="H26" s="3"/>
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>1159</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>1161</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>1160</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>1162</v>
+      </c>
       <c r="I26" s="3"/>
     </row>
     <row r="27" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="4"/>
+      <c r="A27" s="4">
+        <v>26</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C27" t="s">
+        <v>981</v>
+      </c>
+      <c r="D27" t="s">
+        <v>827</v>
+      </c>
+      <c r="E27" t="s">
+        <v>456</v>
+      </c>
+      <c r="F27" t="s">
+        <v>1164</v>
+      </c>
+      <c r="G27" t="s">
+        <v>456</v>
+      </c>
+      <c r="H27" t="s">
+        <v>1165</v>
+      </c>
     </row>
     <row r="28" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="4"/>
+      <c r="A28" s="4">
+        <v>27</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1166</v>
+      </c>
+      <c r="C28" t="s">
+        <v>6</v>
+      </c>
+      <c r="D28" t="s">
+        <v>57</v>
+      </c>
+      <c r="E28" t="s">
+        <v>55</v>
+      </c>
+      <c r="F28" t="s">
+        <v>833</v>
+      </c>
+      <c r="G28" t="s">
+        <v>57</v>
+      </c>
+      <c r="H28" t="s">
+        <v>1167</v>
+      </c>
     </row>
     <row r="29" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="4"/>
+      <c r="A29" s="4">
+        <v>28</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1168</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1169</v>
+      </c>
+      <c r="D29" t="s">
+        <v>1170</v>
+      </c>
+      <c r="E29" t="s">
+        <v>611</v>
+      </c>
+      <c r="F29" t="s">
+        <v>1171</v>
+      </c>
+      <c r="G29" t="s">
+        <v>1170</v>
+      </c>
+      <c r="H29" t="s">
+        <v>1172</v>
+      </c>
     </row>
     <row r="30" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="4"/>
+      <c r="A30" s="4">
+        <v>29</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C30" t="s">
+        <v>61</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1174</v>
+      </c>
+      <c r="E30" t="s">
+        <v>1175</v>
+      </c>
+      <c r="F30" t="s">
+        <v>62</v>
+      </c>
+      <c r="G30" t="s">
+        <v>1174</v>
+      </c>
+      <c r="H30" t="s">
+        <v>1176</v>
+      </c>
     </row>
     <row r="31" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="4"/>
+      <c r="A31" s="4">
+        <v>30</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1178</v>
+      </c>
+      <c r="D31" t="s">
+        <v>1179</v>
+      </c>
+      <c r="E31" t="s">
+        <v>1180</v>
+      </c>
+      <c r="F31" t="s">
+        <v>1181</v>
+      </c>
+      <c r="G31" t="s">
+        <v>1178</v>
+      </c>
+      <c r="H31" t="s">
+        <v>1182</v>
+      </c>
     </row>
     <row r="32" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="4"/>
-    </row>
-    <row r="33" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="4"/>
-    </row>
-    <row r="34" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="4"/>
-    </row>
-    <row r="35" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="4"/>
-    </row>
-    <row r="36" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="4"/>
-    </row>
-    <row r="37" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="4"/>
-    </row>
-    <row r="38" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="4"/>
-    </row>
-    <row r="39" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="4"/>
-    </row>
-    <row r="40" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="4"/>
-    </row>
-    <row r="41" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="4"/>
-    </row>
-    <row r="42" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="43" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="44" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="45" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="46" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="47" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="48" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+      <c r="A32" s="4">
+        <v>31</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C32" t="s">
+        <v>50</v>
+      </c>
+      <c r="D32" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" t="s">
+        <v>23</v>
+      </c>
+      <c r="F32" t="s">
+        <v>1184</v>
+      </c>
+      <c r="G32" t="s">
+        <v>1184</v>
+      </c>
+      <c r="H32" t="s">
+        <v>1185</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="4">
+        <v>32</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C33" t="s">
+        <v>29</v>
+      </c>
+      <c r="D33" t="s">
+        <v>67</v>
+      </c>
+      <c r="E33" t="s">
+        <v>68</v>
+      </c>
+      <c r="F33" t="s">
+        <v>59</v>
+      </c>
+      <c r="G33" t="s">
+        <v>68</v>
+      </c>
+      <c r="H33" t="s">
+        <v>1187</v>
+      </c>
+      <c r="I33" t="s">
+        <v>1210</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="4">
+        <v>33</v>
+      </c>
+      <c r="B34" t="s">
+        <v>627</v>
+      </c>
+      <c r="C34" t="s">
+        <v>628</v>
+      </c>
+      <c r="D34" t="s">
+        <v>629</v>
+      </c>
+      <c r="E34" t="s">
+        <v>630</v>
+      </c>
+      <c r="F34" t="s">
+        <v>631</v>
+      </c>
+      <c r="G34" t="s">
+        <v>629</v>
+      </c>
+      <c r="H34" t="s">
+        <v>1188</v>
+      </c>
+      <c r="I34" t="s">
+        <v>1211</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="4">
+        <v>34</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1190</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1191</v>
+      </c>
+      <c r="E35" t="s">
+        <v>1192</v>
+      </c>
+      <c r="F35" t="s">
+        <v>1193</v>
+      </c>
+      <c r="G35" t="s">
+        <v>1192</v>
+      </c>
+      <c r="H35" t="s">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="4">
+        <v>35</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C36" t="s">
+        <v>29</v>
+      </c>
+      <c r="D36" t="s">
+        <v>67</v>
+      </c>
+      <c r="E36" t="s">
+        <v>68</v>
+      </c>
+      <c r="F36" t="s">
+        <v>59</v>
+      </c>
+      <c r="G36" t="s">
+        <v>67</v>
+      </c>
+      <c r="H36" t="s">
+        <v>1196</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="4">
+        <v>36</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1198</v>
+      </c>
+      <c r="D37" t="s">
+        <v>51</v>
+      </c>
+      <c r="E37" t="s">
+        <v>578</v>
+      </c>
+      <c r="F37" t="s">
+        <v>34</v>
+      </c>
+      <c r="G37" t="s">
+        <v>51</v>
+      </c>
+      <c r="H37" t="s">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A38" s="4">
+        <v>37</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C38" t="s">
+        <v>628</v>
+      </c>
+      <c r="D38" t="s">
+        <v>629</v>
+      </c>
+      <c r="E38" t="s">
+        <v>630</v>
+      </c>
+      <c r="F38" t="s">
+        <v>631</v>
+      </c>
+      <c r="G38" t="s">
+        <v>630</v>
+      </c>
+      <c r="H38" t="s">
+        <v>1201</v>
+      </c>
+      <c r="I38" t="s">
+        <v>1212</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="4">
+        <v>38</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C39" t="s">
+        <v>251</v>
+      </c>
+      <c r="D39" t="s">
+        <v>814</v>
+      </c>
+      <c r="E39" t="s">
+        <v>26</v>
+      </c>
+      <c r="F39" t="s">
+        <v>27</v>
+      </c>
+      <c r="G39" t="s">
+        <v>251</v>
+      </c>
+      <c r="H39" t="s">
+        <v>1203</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A40" s="4">
+        <v>39</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C40" t="s">
+        <v>628</v>
+      </c>
+      <c r="D40" t="s">
+        <v>629</v>
+      </c>
+      <c r="E40" t="s">
+        <v>630</v>
+      </c>
+      <c r="F40" t="s">
+        <v>631</v>
+      </c>
+      <c r="G40" t="s">
+        <v>628</v>
+      </c>
+      <c r="H40" t="s">
+        <v>1205</v>
+      </c>
+      <c r="I40" t="s">
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="4">
+        <v>40</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1207</v>
+      </c>
+      <c r="D41" t="s">
+        <v>1028</v>
+      </c>
+      <c r="E41" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F41" t="s">
+        <v>1208</v>
+      </c>
+      <c r="G41" t="s">
+        <v>1028</v>
+      </c>
+      <c r="H41" t="s">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="43" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="44" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="45" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="46" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="47" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="48" spans="1:9" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
